--- a/Data_Dictionary.xlsx
+++ b/Data_Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Messy CSV to Power BI Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/palaksingh/Documents/superstore project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EBC261C-9202-4C1C-9649-8734FB261FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6811338-AF42-C947-BB9C-DBB8C51D39B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{AAF47BE9-46BF-4B61-AAA3-399AD5248698}"/>
+    <workbookView xWindow="13620" yWindow="660" windowWidth="15780" windowHeight="16820" xr2:uid="{AAF47BE9-46BF-4B61-AAA3-399AD5248698}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="67">
   <si>
     <t>Column Name</t>
   </si>
@@ -222,6 +222,24 @@
   </si>
   <si>
     <t>Combined key used to connect geography data with FactSales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FactSales </t>
+  </si>
+  <si>
+    <t>DimCustomer</t>
+  </si>
+  <si>
+    <t>DimProduct</t>
+  </si>
+  <si>
+    <t>DimGeography</t>
+  </si>
+  <si>
+    <t>DimDate</t>
   </si>
 </sst>
 </file>
@@ -279,6 +297,18 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -297,18 +327,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -323,12 +341,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CCE05CAF-BA62-4D73-993E-DBCDF57D1C25}" name="Table1" displayName="Table1" ref="A1:C28" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:C28" xr:uid="{CCE05CAF-BA62-4D73-993E-DBCDF57D1C25}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CCE05CAF-BA62-4D73-993E-DBCDF57D1C25}" name="Table1" displayName="Table1" ref="B1:D28" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="B1:D28" xr:uid="{CCE05CAF-BA62-4D73-993E-DBCDF57D1C25}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B52A66D0-896A-4BA0-A7B3-988E1D146569}" name="Column Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{165F422C-6895-481E-81F3-153695D0D4A7}" name="Data Type" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{02B6F69A-A679-434C-ACE0-E0DFDF93C345}" name="Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B52A66D0-896A-4BA0-A7B3-988E1D146569}" name="Column Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{165F422C-6895-481E-81F3-153695D0D4A7}" name="Data Type" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{02B6F69A-A679-434C-ACE0-E0DFDF93C345}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -651,319 +669,404 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C16CE6-B7B6-439A-80A3-7F7F20942AE3}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>60</v>
       </c>
     </row>
